--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>90893</v>
+        <v>90899</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -975,10 +975,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610876</v>
+        <v>610872</v>
       </c>
       <c r="R4" t="n">
-        <v>6799574</v>
+        <v>6799576</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>90899</v>
+        <v>90906</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -776,14 +776,9 @@
           <t>Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Grov tall, på död gren.</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris # Grov tall, på död gren.</t>
+          <t>Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>90957</v>
+        <v>90975</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>90908</v>
+        <v>91207</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,11 +944,6 @@
       </c>
       <c r="E4" t="n">
         <v>4217</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Blodticka</t>
-        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -966,17 +961,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Strand, Hls</t>
+          <t>Granskärs våtmark, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>610872</v>
+        <v>610867</v>
       </c>
       <c r="R4" t="n">
-        <v>6799576</v>
+        <v>6799581</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1023,35 +1018,25 @@
           <t>brynmiljö tall</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>vanlig tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris var. sylvestris</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>Gren</t>
+          <t>på gren</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris # Gren</t>
+          <t>på gren</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91207</v>
+        <v>91220</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,6 +944,11 @@
       </c>
       <c r="E4" t="n">
         <v>4217</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91220</v>
+        <v>91233</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91233</v>
+        <v>91234</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91234</v>
+        <v>91235</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91235</v>
+        <v>91238</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91238</v>
+        <v>91341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -930,7 +930,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91341</v>
+        <v>91345</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>90975</v>
+        <v>91353</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -776,20 +776,25 @@
           <t>Pinus sylvestris var. sylvestris</t>
         </is>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Uppe i tallen</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris</t>
+          <t>Pinus sylvestris var. sylvestris # Uppe i tallen</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -930,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91345</v>
+        <v>91353</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1020,7 +1025,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>brynmiljö tall</t>
+          <t>skogskant med tall</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1051,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91262</v>
+        <v>91648</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1134,14 +1139,9 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>tallsluttning</t>
+          <t>skogsdunge sluttning tall</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1156,23 +1156,23 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>barklös, murken tallåga</t>
+          <t>undersidan murken barklös låga av tall</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Pinus sylvestris var. sylvestris # barklös, murken tallåga</t>
+          <t>Pinus sylvestris var. sylvestris # undersidan murken barklös låga av tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>90444</v>
+        <v>91852</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granskärs våtmark, Söderhamn, Hls</t>
+          <t>Strand, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -1280,18 +1280,18 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>blandskog mossig slänt med tall och gran</t>
+          <t>blandskog mossig slänt med tall gran vid våtmark</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Andreas Nilsson</t>
+          <t>Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Nilsson, Max Rosendahl</t>
+          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91353</v>
+        <v>91356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91353</v>
+        <v>91356</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91648</v>
+        <v>91651</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
+        <v>91855</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91356</v>
+        <v>91358</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>91358</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91651</v>
+        <v>91653</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91855</v>
+        <v>91857</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91358</v>
+        <v>91364</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91358</v>
+        <v>91364</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91653</v>
+        <v>91659</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91857</v>
+        <v>91863</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Strand, Hls</t>
+          <t>Norr Granskärs våtmark, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91367</v>
+        <v>91384</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91384</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91662</v>
+        <v>91679</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91866</v>
+        <v>91883</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91384</v>
+        <v>91389</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91384</v>
+        <v>91389</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91679</v>
+        <v>91684</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91883</v>
+        <v>91888</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>100893131</v>
       </c>
       <c r="B2" t="n">
-        <v>91389</v>
+        <v>91391</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
         <v>101113537</v>
       </c>
       <c r="B4" t="n">
-        <v>91389</v>
+        <v>91391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91684</v>
+        <v>91686</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1182,7 +1182,7 @@
         <v>112017318</v>
       </c>
       <c r="B6" t="n">
-        <v>91888</v>
+        <v>91890</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
+          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -1291,7 +1291,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Max Rosendahl, Andreas Thomas Nilsson</t>
+          <t>Andreas Thomas Nilsson, Max Rosendahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 39885-2023 artfynd.xlsx
+++ b/artfynd/A 39885-2023 artfynd.xlsx
@@ -1056,7 +1056,7 @@
         <v>108749507</v>
       </c>
       <c r="B5" t="n">
-        <v>91708</v>
+        <v>91868</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
